--- a/controle/controle.xlsx
+++ b/controle/controle.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="99">
   <si>
     <t>ENVIRONNEMENT DU CONTRÔLE</t>
   </si>
@@ -296,6 +296,18 @@
   </si>
   <si>
     <t>RAS</t>
+  </si>
+  <si>
+    <t>23/03/26</t>
+  </si>
+  <si>
+    <t>138</t>
+  </si>
+  <si>
+    <t>Freyming</t>
+  </si>
+  <si>
+    <t>12:30</t>
   </si>
 </sst>
 </file>
@@ -846,7 +858,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AW5"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -1566,6 +1578,155 @@
         <v>79</v>
       </c>
     </row>
+    <row r="6" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="A6" s="29" t="s">
+        <v>95</v>
+      </c>
+      <c r="B6" s="29" t="s">
+        <v>96</v>
+      </c>
+      <c r="C6" s="29" t="s">
+        <v>81</v>
+      </c>
+      <c r="D6" s="29" t="s">
+        <v>97</v>
+      </c>
+      <c r="E6" s="29" t="s">
+        <v>98</v>
+      </c>
+      <c r="F6" s="29" t="s">
+        <v>68</v>
+      </c>
+      <c r="G6" s="29" t="s">
+        <v>69</v>
+      </c>
+      <c r="H6" s="29">
+        <v>0</v>
+      </c>
+      <c r="I6" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="J6" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="K6" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="L6" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="M6" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="N6" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="O6" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="P6" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q6" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="R6" s="29" t="s">
+        <v>72</v>
+      </c>
+      <c r="S6" s="29" t="s">
+        <v>73</v>
+      </c>
+      <c r="T6" s="29" t="s">
+        <v>73</v>
+      </c>
+      <c r="U6" s="29" t="s">
+        <v>73</v>
+      </c>
+      <c r="V6" s="29" t="s">
+        <v>72</v>
+      </c>
+      <c r="W6" s="29" t="s">
+        <v>72</v>
+      </c>
+      <c r="X6" s="29" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y6" s="29">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="29">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="AB6" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="AC6" s="29" t="s">
+        <v>74</v>
+      </c>
+      <c r="AD6" s="29" t="s">
+        <v>75</v>
+      </c>
+      <c r="AE6" s="29" t="s">
+        <v>89</v>
+      </c>
+      <c r="AF6" s="29" t="s">
+        <v>72</v>
+      </c>
+      <c r="AG6" s="29" t="s">
+        <v>77</v>
+      </c>
+      <c r="AH6" s="29" t="s">
+        <v>72</v>
+      </c>
+      <c r="AI6" s="29" t="s">
+        <v>72</v>
+      </c>
+      <c r="AJ6" s="29" t="s">
+        <v>72</v>
+      </c>
+      <c r="AK6" s="29" t="s">
+        <v>72</v>
+      </c>
+      <c r="AL6" s="29" t="s">
+        <v>72</v>
+      </c>
+      <c r="AM6" s="29" t="s">
+        <v>72</v>
+      </c>
+      <c r="AN6" s="29" t="s">
+        <v>78</v>
+      </c>
+      <c r="AO6" s="29" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP6" s="29" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ6" s="29" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR6" s="29" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS6" s="29" t="s">
+        <v>75</v>
+      </c>
+      <c r="AT6" s="29" t="s">
+        <v>73</v>
+      </c>
+      <c r="AU6" s="29" t="s">
+        <v>73</v>
+      </c>
+      <c r="AV6" s="29" t="s">
+        <v>75</v>
+      </c>
+      <c r="AW6" s="29" t="s">
+        <v>79</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="11">
     <mergeCell ref="A1:I1"/>

--- a/controle/controle.xlsx
+++ b/controle/controle.xlsx
@@ -3,6 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+  <bookViews>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
+  </bookViews>
   <sheets>
     <sheet sheetId="1" name="Controles" state="visible" r:id="rId4"/>
   </sheets>
@@ -11,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="569" uniqueCount="141">
   <si>
     <t>ENVIRONNEMENT DU CONTRÔLE</t>
   </si>
@@ -202,112 +205,238 @@
     <t>Nom contrôleur</t>
   </si>
   <si>
-    <t>22/03/26</t>
-  </si>
-  <si>
-    <t>125</t>
-  </si>
-  <si>
-    <t>casc — Lr</t>
-  </si>
-  <si>
-    <t>poli</t>
-  </si>
-  <si>
-    <t>19:06</t>
-  </si>
-  <si>
-    <t>—</t>
-  </si>
-  <si>
-    <t>Non applicable — car non passé (sans conducteur)</t>
-  </si>
-  <si>
-    <t>Oui</t>
+    <t>14/04/26</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>rgeFluo57 — Lr</t>
+  </si>
+  <si>
+    <t>Fareberviller rue de sarreguemine</t>
+  </si>
+  <si>
+    <t>11:01</t>
+  </si>
+  <si>
+    <t>10:57</t>
+  </si>
+  <si>
+    <t>Klingler</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>Non observable</t>
+  </si>
+  <si>
+    <t>Juste zebra</t>
+  </si>
+  <si>
+    <t>rgeFluo57</t>
+  </si>
+  <si>
+    <t>Lr</t>
+  </si>
+  <si>
+    <t>beau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fissure pare-brise avant </t>
+  </si>
+  <si>
+    <t>Ras</t>
+  </si>
+  <si>
+    <t>BANGOURA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Farebersviller rue de sarreguemine </t>
+  </si>
+  <si>
+    <t>11:11</t>
+  </si>
+  <si>
+    <t>11:12</t>
+  </si>
+  <si>
+    <t>Bertan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Juste un zébra </t>
+  </si>
+  <si>
+    <t>Pas de machine</t>
+  </si>
+  <si>
+    <t>138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Freyming gare routière </t>
+  </si>
+  <si>
+    <t>14:26</t>
+  </si>
+  <si>
+    <t>14:35</t>
+  </si>
+  <si>
+    <t>Berisa</t>
+  </si>
+  <si>
+    <t>Abris bus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Horaire caché par ceux de la 123 et j'ai pas de clé </t>
+  </si>
+  <si>
+    <t>Tout fonctionne</t>
+  </si>
+  <si>
+    <t>12/05/26</t>
+  </si>
+  <si>
+    <t>129</t>
+  </si>
+  <si>
+    <t>Gare routière behren</t>
+  </si>
+  <si>
+    <t>08:12</t>
+  </si>
+  <si>
+    <t>08:13</t>
+  </si>
+  <si>
+    <t>Fatal yabriudi</t>
   </si>
   <si>
     <t>NC</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
-    <t>M</t>
-  </si>
-  <si>
-    <t>Non observable</t>
-  </si>
-  <si>
-    <t>Car non passé — contrôle véhicule non réalisé.</t>
-  </si>
-  <si>
-    <t>casc</t>
-  </si>
-  <si>
-    <t>Lr</t>
-  </si>
-  <si>
-    <t>beau</t>
-  </si>
-  <si>
-    <t>BANGOURA</t>
-  </si>
-  <si>
-    <t>129</t>
-  </si>
-  <si>
-    <t>rgeFluo57 — Lr</t>
-  </si>
-  <si>
-    <t>sarreguemines</t>
-  </si>
-  <si>
-    <t>19:10</t>
-  </si>
-  <si>
-    <t>19:07</t>
-  </si>
-  <si>
-    <t>BANGOURA Ibrahima</t>
-  </si>
-  <si>
-    <t>C</t>
+    <t>Changement de poteau donc plus d'affiches</t>
+  </si>
+  <si>
+    <t>Behren- Rue des roses</t>
+  </si>
+  <si>
+    <t>08:37</t>
+  </si>
+  <si>
+    <t>08:35</t>
+  </si>
+  <si>
+    <t>Temmar</t>
+  </si>
+  <si>
+    <t>13/05/26</t>
+  </si>
+  <si>
+    <t>Hombourg haut - chateau</t>
+  </si>
+  <si>
+    <t>08:14</t>
+  </si>
+  <si>
+    <t>08:15</t>
+  </si>
+  <si>
+    <t>Ouknin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Freyming - Cité administrative </t>
+  </si>
+  <si>
+    <t>08:33</t>
+  </si>
+  <si>
+    <t>Chahid</t>
   </si>
   <si>
     <t>Poteau arrêt</t>
   </si>
   <si>
-    <t>ras</t>
-  </si>
-  <si>
-    <t>rgeFluo57</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>IPPLING</t>
-  </si>
-  <si>
-    <t>20:33</t>
-  </si>
-  <si>
-    <t>20:31</t>
+    <t>Pas de panneau</t>
   </si>
   <si>
     <t>RAS</t>
   </si>
   <si>
-    <t>23/03/26</t>
-  </si>
-  <si>
-    <t>138</t>
-  </si>
-  <si>
-    <t>Freyming</t>
-  </si>
-  <si>
-    <t>12:30</t>
+    <t>18/05/26</t>
+  </si>
+  <si>
+    <t>07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Creutzwald-Gare routière </t>
+  </si>
+  <si>
+    <t>06:53</t>
+  </si>
+  <si>
+    <t>06:50</t>
+  </si>
+  <si>
+    <t>Schuler</t>
+  </si>
+  <si>
+    <t>04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boulay- Place du marché </t>
+  </si>
+  <si>
+    <t>07:45</t>
+  </si>
+  <si>
+    <t>07:50</t>
+  </si>
+  <si>
+    <t>Dolveck</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Creutzwald- Gare routière </t>
+  </si>
+  <si>
+    <t>09:01</t>
+  </si>
+  <si>
+    <t>09:02</t>
+  </si>
+  <si>
+    <t>Brouck</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pas de machine </t>
+  </si>
+  <si>
+    <t>L6</t>
+  </si>
+  <si>
+    <t>casas — transavold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'Hopital - Place nasseau </t>
+  </si>
+  <si>
+    <t>09:24</t>
+  </si>
+  <si>
+    <t>09:26</t>
+  </si>
+  <si>
+    <t>Eren</t>
+  </si>
+  <si>
+    <t>casas</t>
+  </si>
+  <si>
+    <t>transavold</t>
   </si>
 </sst>
 </file>
@@ -325,12 +454,15 @@
     <font>
       <b/>
       <sz val="10"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <sz val="10"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <sz val="9"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="16">
@@ -858,8 +990,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AW6"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <dimension ref="A1:AW13"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" defaultColWidth="9.140625"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -903,7 +1035,7 @@
     <col min="49" max="49" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="1" ht="27.95" customHeight="1" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -982,7 +1114,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" ht="56" customHeight="1" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="2" ht="56.1" customHeight="1" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A2" s="15" t="s">
         <v>14</v>
       </c>
@@ -1154,16 +1286,16 @@
         <v>69</v>
       </c>
       <c r="H3" s="29">
-        <v>0</v>
+        <v>103789</v>
       </c>
       <c r="I3" s="29" t="s">
         <v>70</v>
       </c>
       <c r="J3" s="29" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K3" s="29" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L3" s="29" t="s">
         <v>71</v>
@@ -1184,97 +1316,97 @@
         <v>71</v>
       </c>
       <c r="R3" s="29" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="S3" s="29" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="T3" s="29" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="U3" s="29" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="V3" s="29" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="W3" s="29" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="X3" s="29" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="Y3" s="29">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Z3" s="29">
         <v>0</v>
       </c>
       <c r="AA3" s="29" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AB3" s="29" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AC3" s="29" t="s">
+        <v>72</v>
+      </c>
+      <c r="AD3" s="29" t="s">
+        <v>73</v>
+      </c>
+      <c r="AE3" s="29" t="s">
         <v>74</v>
       </c>
-      <c r="AD3" s="29" t="s">
+      <c r="AF3" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="AG3" s="29" t="s">
         <v>75</v>
       </c>
-      <c r="AE3" s="29" t="s">
+      <c r="AH3" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="AI3" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="AJ3" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="AK3" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="AL3" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="AM3" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="AN3" s="29" t="s">
         <v>76</v>
       </c>
-      <c r="AF3" s="29" t="s">
-        <v>72</v>
-      </c>
-      <c r="AG3" s="29" t="s">
-        <v>72</v>
-      </c>
-      <c r="AH3" s="29" t="s">
+      <c r="AO3" s="29" t="s">
         <v>77</v>
       </c>
-      <c r="AI3" s="29" t="s">
-        <v>72</v>
-      </c>
-      <c r="AJ3" s="29" t="s">
-        <v>72</v>
-      </c>
-      <c r="AK3" s="29" t="s">
-        <v>72</v>
-      </c>
-      <c r="AL3" s="29" t="s">
-        <v>72</v>
-      </c>
-      <c r="AM3" s="29" t="s">
-        <v>72</v>
-      </c>
-      <c r="AN3" s="29" t="s">
-        <v>78</v>
-      </c>
-      <c r="AO3" s="29" t="s">
-        <v>75</v>
-      </c>
       <c r="AP3" s="29" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="AQ3" s="29" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="AR3" s="29" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="AS3" s="29" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="AT3" s="29" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="AU3" s="29" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="AV3" s="29" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="AW3" s="29" t="s">
         <v>79</v>
@@ -1285,145 +1417,145 @@
         <v>63</v>
       </c>
       <c r="B4" s="29" t="s">
+        <v>64</v>
+      </c>
+      <c r="C4" s="29" t="s">
+        <v>65</v>
+      </c>
+      <c r="D4" s="29" t="s">
         <v>80</v>
       </c>
-      <c r="C4" s="29" t="s">
+      <c r="E4" s="29" t="s">
         <v>81</v>
       </c>
-      <c r="D4" s="29" t="s">
+      <c r="F4" s="29" t="s">
         <v>82</v>
       </c>
-      <c r="E4" s="29" t="s">
+      <c r="G4" s="29" t="s">
         <v>83</v>
       </c>
-      <c r="F4" s="29" t="s">
-        <v>84</v>
-      </c>
-      <c r="G4" s="29" t="s">
-        <v>85</v>
-      </c>
       <c r="H4" s="29">
-        <v>23959</v>
+        <v>106560</v>
       </c>
       <c r="I4" s="29" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J4" s="29" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="K4" s="29" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="L4" s="29" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="M4" s="29" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="N4" s="29" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="O4" s="29" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="P4" s="29" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="Q4" s="29" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="R4" s="29" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="S4" s="29" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="T4" s="29" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="U4" s="29" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="V4" s="29" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="W4" s="29" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="X4" s="29" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="Y4" s="29">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="Z4" s="29">
         <v>0</v>
       </c>
       <c r="AA4" s="29" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="AB4" s="29" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="AC4" s="29" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="AD4" s="29" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="AE4" s="29" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="AF4" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="AG4" s="29" t="s">
+        <v>75</v>
+      </c>
+      <c r="AH4" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="AI4" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="AJ4" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="AK4" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="AL4" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="AM4" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="AN4" s="29" t="s">
+        <v>76</v>
+      </c>
+      <c r="AO4" s="29" t="s">
+        <v>78</v>
+      </c>
+      <c r="AP4" s="29" t="s">
         <v>72</v>
       </c>
-      <c r="AG4" s="29" t="s">
-        <v>77</v>
-      </c>
-      <c r="AH4" s="29" t="s">
-        <v>72</v>
-      </c>
-      <c r="AI4" s="29" t="s">
-        <v>72</v>
-      </c>
-      <c r="AJ4" s="29" t="s">
-        <v>72</v>
-      </c>
-      <c r="AK4" s="29" t="s">
-        <v>72</v>
-      </c>
-      <c r="AL4" s="29" t="s">
-        <v>72</v>
-      </c>
-      <c r="AM4" s="29" t="s">
-        <v>72</v>
-      </c>
-      <c r="AN4" s="29" t="s">
-        <v>78</v>
-      </c>
-      <c r="AO4" s="29" t="s">
-        <v>88</v>
-      </c>
-      <c r="AP4" s="29" t="s">
-        <v>86</v>
-      </c>
       <c r="AQ4" s="29" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="AR4" s="29" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="AS4" s="29" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="AT4" s="29" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="AU4" s="29" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="AV4" s="29" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AW4" s="29" t="s">
         <v>79</v>
@@ -1434,145 +1566,145 @@
         <v>63</v>
       </c>
       <c r="B5" s="29" t="s">
+        <v>86</v>
+      </c>
+      <c r="C5" s="29" t="s">
+        <v>65</v>
+      </c>
+      <c r="D5" s="29" t="s">
+        <v>87</v>
+      </c>
+      <c r="E5" s="29" t="s">
+        <v>88</v>
+      </c>
+      <c r="F5" s="29" t="s">
+        <v>89</v>
+      </c>
+      <c r="G5" s="29" t="s">
         <v>90</v>
       </c>
-      <c r="C5" s="29" t="s">
-        <v>81</v>
-      </c>
-      <c r="D5" s="29" t="s">
+      <c r="H5" s="29">
+        <v>104420</v>
+      </c>
+      <c r="I5" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="J5" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="K5" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="L5" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="M5" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="N5" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="O5" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="P5" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q5" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="R5" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="S5" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="T5" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="U5" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="V5" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="W5" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="X5" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="Y5" s="29">
+        <v>7</v>
+      </c>
+      <c r="Z5" s="29">
+        <v>0</v>
+      </c>
+      <c r="AA5" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="AB5" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="AC5" s="29" t="s">
         <v>91</v>
       </c>
-      <c r="E5" s="29" t="s">
+      <c r="AD5" s="29" t="s">
         <v>92</v>
       </c>
-      <c r="F5" s="29" t="s">
+      <c r="AE5" s="29" t="s">
+        <v>74</v>
+      </c>
+      <c r="AF5" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="AG5" s="29" t="s">
+        <v>75</v>
+      </c>
+      <c r="AH5" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="AI5" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="AJ5" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="AK5" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="AL5" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="AM5" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="AN5" s="29" t="s">
+        <v>76</v>
+      </c>
+      <c r="AO5" s="29" t="s">
+        <v>78</v>
+      </c>
+      <c r="AP5" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="AQ5" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="AR5" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="AS5" s="29" t="s">
         <v>93</v>
       </c>
-      <c r="G5" s="29" t="s">
-        <v>79</v>
-      </c>
-      <c r="H5" s="29">
-        <v>23959</v>
-      </c>
-      <c r="I5" s="29" t="s">
-        <v>72</v>
-      </c>
-      <c r="J5" s="29" t="s">
-        <v>86</v>
-      </c>
-      <c r="K5" s="29" t="s">
-        <v>86</v>
-      </c>
-      <c r="L5" s="29" t="s">
-        <v>86</v>
-      </c>
-      <c r="M5" s="29" t="s">
-        <v>86</v>
-      </c>
-      <c r="N5" s="29" t="s">
-        <v>86</v>
-      </c>
-      <c r="O5" s="29" t="s">
-        <v>86</v>
-      </c>
-      <c r="P5" s="29" t="s">
-        <v>86</v>
-      </c>
-      <c r="Q5" s="29" t="s">
-        <v>86</v>
-      </c>
-      <c r="R5" s="29" t="s">
-        <v>72</v>
-      </c>
-      <c r="S5" s="29" t="s">
-        <v>86</v>
-      </c>
-      <c r="T5" s="29" t="s">
-        <v>86</v>
-      </c>
-      <c r="U5" s="29" t="s">
-        <v>86</v>
-      </c>
-      <c r="V5" s="29" t="s">
-        <v>72</v>
-      </c>
-      <c r="W5" s="29" t="s">
-        <v>72</v>
-      </c>
-      <c r="X5" s="29" t="s">
-        <v>72</v>
-      </c>
-      <c r="Y5" s="29">
-        <v>20</v>
-      </c>
-      <c r="Z5" s="29">
-        <v>1</v>
-      </c>
-      <c r="AA5" s="29" t="s">
-        <v>86</v>
-      </c>
-      <c r="AB5" s="29" t="s">
-        <v>86</v>
-      </c>
-      <c r="AC5" s="29" t="s">
-        <v>87</v>
-      </c>
-      <c r="AD5" s="29" t="s">
-        <v>94</v>
-      </c>
-      <c r="AE5" s="29" t="s">
-        <v>89</v>
-      </c>
-      <c r="AF5" s="29" t="s">
-        <v>72</v>
-      </c>
-      <c r="AG5" s="29" t="s">
-        <v>77</v>
-      </c>
-      <c r="AH5" s="29" t="s">
-        <v>72</v>
-      </c>
-      <c r="AI5" s="29" t="s">
-        <v>72</v>
-      </c>
-      <c r="AJ5" s="29" t="s">
-        <v>72</v>
-      </c>
-      <c r="AK5" s="29" t="s">
-        <v>72</v>
-      </c>
-      <c r="AL5" s="29" t="s">
-        <v>72</v>
-      </c>
-      <c r="AM5" s="29" t="s">
-        <v>72</v>
-      </c>
-      <c r="AN5" s="29" t="s">
-        <v>78</v>
-      </c>
-      <c r="AO5" s="29" t="s">
-        <v>94</v>
-      </c>
-      <c r="AP5" s="29" t="s">
-        <v>86</v>
-      </c>
-      <c r="AQ5" s="29" t="s">
-        <v>86</v>
-      </c>
-      <c r="AR5" s="29" t="s">
-        <v>86</v>
-      </c>
-      <c r="AS5" s="29" t="s">
-        <v>94</v>
-      </c>
       <c r="AT5" s="29" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="AU5" s="29" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="AV5" s="29" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="AW5" s="29" t="s">
         <v>79</v>
@@ -1580,150 +1712,1193 @@
     </row>
     <row r="6" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A6" s="29" t="s">
+        <v>94</v>
+      </c>
+      <c r="B6" s="29" t="s">
         <v>95</v>
       </c>
-      <c r="B6" s="29" t="s">
+      <c r="C6" s="29" t="s">
+        <v>65</v>
+      </c>
+      <c r="D6" s="29" t="s">
         <v>96</v>
       </c>
-      <c r="C6" s="29" t="s">
-        <v>81</v>
-      </c>
-      <c r="D6" s="29" t="s">
+      <c r="E6" s="29" t="s">
         <v>97</v>
       </c>
-      <c r="E6" s="29" t="s">
+      <c r="F6" s="29" t="s">
         <v>98</v>
       </c>
-      <c r="F6" s="29" t="s">
-        <v>68</v>
-      </c>
       <c r="G6" s="29" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="H6" s="29">
+        <v>109047</v>
+      </c>
+      <c r="I6" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="J6" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="K6" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="L6" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="M6" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="N6" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="O6" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="P6" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q6" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="R6" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="S6" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="T6" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="U6" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="V6" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="W6" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="X6" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="Y6" s="29">
+        <v>12</v>
+      </c>
+      <c r="Z6" s="29">
+        <v>2</v>
+      </c>
+      <c r="AA6" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="AB6" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="AC6" s="29" t="s">
+        <v>91</v>
+      </c>
+      <c r="AD6" s="29" t="s">
+        <v>101</v>
+      </c>
+      <c r="AE6" s="29" t="s">
+        <v>74</v>
+      </c>
+      <c r="AF6" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="AG6" s="29" t="s">
+        <v>75</v>
+      </c>
+      <c r="AH6" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="AI6" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="AJ6" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="AK6" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="AL6" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="AM6" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="AN6" s="29" t="s">
+        <v>76</v>
+      </c>
+      <c r="AO6" s="29" t="s">
+        <v>78</v>
+      </c>
+      <c r="AP6" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="AQ6" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="AR6" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="AS6" s="29" t="s">
+        <v>78</v>
+      </c>
+      <c r="AT6" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="AU6" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="AV6" s="29" t="s">
+        <v>78</v>
+      </c>
+      <c r="AW6" s="29" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="7" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="A7" s="29" t="s">
+        <v>94</v>
+      </c>
+      <c r="B7" s="29" t="s">
+        <v>95</v>
+      </c>
+      <c r="C7" s="29" t="s">
+        <v>65</v>
+      </c>
+      <c r="D7" s="29" t="s">
+        <v>102</v>
+      </c>
+      <c r="E7" s="29" t="s">
+        <v>103</v>
+      </c>
+      <c r="F7" s="29" t="s">
+        <v>104</v>
+      </c>
+      <c r="G7" s="29" t="s">
+        <v>105</v>
+      </c>
+      <c r="H7" s="29">
+        <v>109953</v>
+      </c>
+      <c r="I7" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="J7" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="K7" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="L7" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="M7" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="N7" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="O7" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="P7" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q7" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="R7" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="S7" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="T7" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="U7" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="V7" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="W7" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="X7" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="Y7" s="29">
+        <v>19</v>
+      </c>
+      <c r="Z7" s="29">
         <v>0</v>
       </c>
-      <c r="I6" s="29" t="s">
-        <v>70</v>
-      </c>
-      <c r="J6" s="29" t="s">
-        <v>71</v>
-      </c>
-      <c r="K6" s="29" t="s">
-        <v>71</v>
-      </c>
-      <c r="L6" s="29" t="s">
-        <v>71</v>
-      </c>
-      <c r="M6" s="29" t="s">
-        <v>71</v>
-      </c>
-      <c r="N6" s="29" t="s">
-        <v>71</v>
-      </c>
-      <c r="O6" s="29" t="s">
-        <v>71</v>
-      </c>
-      <c r="P6" s="29" t="s">
-        <v>71</v>
-      </c>
-      <c r="Q6" s="29" t="s">
-        <v>71</v>
-      </c>
-      <c r="R6" s="29" t="s">
+      <c r="AA7" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="AB7" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="AC7" s="29" t="s">
+        <v>91</v>
+      </c>
+      <c r="AD7" s="29" t="s">
+        <v>78</v>
+      </c>
+      <c r="AE7" s="29" t="s">
+        <v>74</v>
+      </c>
+      <c r="AF7" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="AG7" s="29" t="s">
+        <v>75</v>
+      </c>
+      <c r="AH7" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="AI7" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="AJ7" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="AK7" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="AL7" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="AM7" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="AN7" s="29" t="s">
+        <v>76</v>
+      </c>
+      <c r="AO7" s="29" t="s">
+        <v>78</v>
+      </c>
+      <c r="AP7" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="AQ7" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="AR7" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="AS7" s="29" t="s">
+        <v>78</v>
+      </c>
+      <c r="AT7" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="AU7" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="AV7" s="29" t="s">
+        <v>78</v>
+      </c>
+      <c r="AW7" s="29" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="8" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="A8" s="29" t="s">
+        <v>106</v>
+      </c>
+      <c r="B8" s="29" t="s">
+        <v>86</v>
+      </c>
+      <c r="C8" s="29" t="s">
+        <v>65</v>
+      </c>
+      <c r="D8" s="29" t="s">
+        <v>107</v>
+      </c>
+      <c r="E8" s="29" t="s">
+        <v>108</v>
+      </c>
+      <c r="F8" s="29" t="s">
+        <v>109</v>
+      </c>
+      <c r="G8" s="29" t="s">
+        <v>110</v>
+      </c>
+      <c r="H8" s="29">
+        <v>24842</v>
+      </c>
+      <c r="I8" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="J8" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="K8" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="L8" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="M8" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="N8" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="O8" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="P8" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q8" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="R8" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="S8" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="T8" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="U8" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="V8" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="W8" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="X8" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="Y8" s="29">
+        <v>11</v>
+      </c>
+      <c r="Z8" s="29">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="AB8" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="AC8" s="29" t="s">
+        <v>91</v>
+      </c>
+      <c r="AD8" s="29" t="s">
+        <v>78</v>
+      </c>
+      <c r="AE8" s="29" t="s">
+        <v>74</v>
+      </c>
+      <c r="AF8" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="AG8" s="29" t="s">
+        <v>75</v>
+      </c>
+      <c r="AH8" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="AI8" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="AJ8" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="AK8" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="AL8" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="AM8" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="AN8" s="29" t="s">
+        <v>76</v>
+      </c>
+      <c r="AO8" s="29" t="s">
+        <v>78</v>
+      </c>
+      <c r="AP8" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="AQ8" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="AR8" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="AS8" s="29" t="s">
+        <v>78</v>
+      </c>
+      <c r="AT8" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="AU8" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="AV8" s="29" t="s">
+        <v>78</v>
+      </c>
+      <c r="AW8" s="29" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="9" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="A9" s="29" t="s">
+        <v>106</v>
+      </c>
+      <c r="B9" s="29" t="s">
+        <v>86</v>
+      </c>
+      <c r="C9" s="29" t="s">
+        <v>65</v>
+      </c>
+      <c r="D9" s="29" t="s">
+        <v>111</v>
+      </c>
+      <c r="E9" s="29" t="s">
+        <v>112</v>
+      </c>
+      <c r="F9" s="29" t="s">
+        <v>112</v>
+      </c>
+      <c r="G9" s="29" t="s">
+        <v>113</v>
+      </c>
+      <c r="H9" s="29">
+        <v>104794</v>
+      </c>
+      <c r="I9" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="J9" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="K9" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="L9" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="M9" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="N9" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="O9" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="P9" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q9" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="R9" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="S9" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="T9" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="U9" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="V9" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="W9" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="X9" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="Y9" s="29">
+        <v>7</v>
+      </c>
+      <c r="Z9" s="29">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="AB9" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="AC9" s="29" t="s">
+        <v>114</v>
+      </c>
+      <c r="AD9" s="29" t="s">
+        <v>115</v>
+      </c>
+      <c r="AE9" s="29" t="s">
+        <v>74</v>
+      </c>
+      <c r="AF9" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="AG9" s="29" t="s">
+        <v>75</v>
+      </c>
+      <c r="AH9" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="AI9" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="AJ9" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="AK9" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="AL9" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="AM9" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="AN9" s="29" t="s">
+        <v>76</v>
+      </c>
+      <c r="AO9" s="29" t="s">
+        <v>116</v>
+      </c>
+      <c r="AP9" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="AQ9" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="AR9" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="AS9" s="29" t="s">
+        <v>116</v>
+      </c>
+      <c r="AT9" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="AU9" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="AV9" s="29" t="s">
+        <v>78</v>
+      </c>
+      <c r="AW9" s="29" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="10" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="A10" s="29" t="s">
+        <v>117</v>
+      </c>
+      <c r="B10" s="29" t="s">
+        <v>118</v>
+      </c>
+      <c r="C10" s="29" t="s">
+        <v>65</v>
+      </c>
+      <c r="D10" s="29" t="s">
+        <v>119</v>
+      </c>
+      <c r="E10" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="F10" s="29" t="s">
+        <v>121</v>
+      </c>
+      <c r="G10" s="29" t="s">
+        <v>122</v>
+      </c>
+      <c r="H10" s="29">
+        <v>120215</v>
+      </c>
+      <c r="I10" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="J10" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="K10" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="L10" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="M10" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="N10" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="O10" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="P10" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q10" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="R10" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="S10" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="T10" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="U10" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="V10" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="W10" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="X10" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="Y10" s="29">
+        <v>0</v>
+      </c>
+      <c r="Z10" s="29">
+        <v>0</v>
+      </c>
+      <c r="AA10" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="AB10" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="AC10" s="29" t="s">
         <v>72</v>
       </c>
-      <c r="S6" s="29" t="s">
-        <v>73</v>
-      </c>
-      <c r="T6" s="29" t="s">
-        <v>73</v>
-      </c>
-      <c r="U6" s="29" t="s">
-        <v>73</v>
-      </c>
-      <c r="V6" s="29" t="s">
+      <c r="AD10" s="29" t="s">
+        <v>78</v>
+      </c>
+      <c r="AE10" s="29" t="s">
+        <v>74</v>
+      </c>
+      <c r="AF10" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="AG10" s="29" t="s">
+        <v>75</v>
+      </c>
+      <c r="AH10" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="AI10" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="AJ10" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="AK10" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="AL10" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="AM10" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="AN10" s="29" t="s">
+        <v>76</v>
+      </c>
+      <c r="AO10" s="29" t="s">
+        <v>78</v>
+      </c>
+      <c r="AP10" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="AQ10" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="AR10" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="AS10" s="29" t="s">
+        <v>78</v>
+      </c>
+      <c r="AT10" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="AU10" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="AV10" s="29" t="s">
+        <v>78</v>
+      </c>
+      <c r="AW10" s="29" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="11" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="A11" s="29" t="s">
+        <v>117</v>
+      </c>
+      <c r="B11" s="29" t="s">
+        <v>123</v>
+      </c>
+      <c r="C11" s="29" t="s">
+        <v>65</v>
+      </c>
+      <c r="D11" s="29" t="s">
+        <v>124</v>
+      </c>
+      <c r="E11" s="29" t="s">
+        <v>125</v>
+      </c>
+      <c r="F11" s="29" t="s">
+        <v>126</v>
+      </c>
+      <c r="G11" s="29" t="s">
+        <v>127</v>
+      </c>
+      <c r="H11" s="29">
+        <v>106590</v>
+      </c>
+      <c r="I11" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="J11" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="K11" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="L11" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="M11" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="N11" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="O11" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="P11" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q11" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="R11" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="S11" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="T11" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="U11" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="V11" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="W11" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="X11" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="Y11" s="29">
+        <v>19</v>
+      </c>
+      <c r="Z11" s="29">
+        <v>0</v>
+      </c>
+      <c r="AA11" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="AB11" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="AC11" s="29" t="s">
+        <v>91</v>
+      </c>
+      <c r="AD11" s="29" t="s">
+        <v>78</v>
+      </c>
+      <c r="AE11" s="29" t="s">
+        <v>74</v>
+      </c>
+      <c r="AF11" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="AG11" s="29" t="s">
+        <v>75</v>
+      </c>
+      <c r="AH11" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="AI11" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="AJ11" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="AK11" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="AL11" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="AM11" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="AN11" s="29" t="s">
+        <v>76</v>
+      </c>
+      <c r="AO11" s="29" t="s">
+        <v>78</v>
+      </c>
+      <c r="AP11" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="AQ11" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="AR11" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="AS11" s="29" t="s">
+        <v>78</v>
+      </c>
+      <c r="AT11" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="AU11" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="AV11" s="29" t="s">
+        <v>78</v>
+      </c>
+      <c r="AW11" s="29" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="12" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="A12" s="29" t="s">
+        <v>117</v>
+      </c>
+      <c r="B12" s="29" t="s">
+        <v>123</v>
+      </c>
+      <c r="C12" s="29" t="s">
+        <v>65</v>
+      </c>
+      <c r="D12" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="E12" s="29" t="s">
+        <v>129</v>
+      </c>
+      <c r="F12" s="29" t="s">
+        <v>130</v>
+      </c>
+      <c r="G12" s="29" t="s">
+        <v>131</v>
+      </c>
+      <c r="H12" s="29">
+        <v>120212</v>
+      </c>
+      <c r="I12" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="J12" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="K12" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="L12" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="M12" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="N12" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="O12" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="P12" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q12" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="R12" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="S12" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="T12" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="U12" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="V12" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="W12" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="X12" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="Y12" s="29">
+        <v>3</v>
+      </c>
+      <c r="Z12" s="29">
+        <v>0</v>
+      </c>
+      <c r="AA12" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="AB12" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="AC12" s="29" t="s">
+        <v>114</v>
+      </c>
+      <c r="AD12" s="29" t="s">
+        <v>78</v>
+      </c>
+      <c r="AE12" s="29" t="s">
+        <v>74</v>
+      </c>
+      <c r="AF12" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="AG12" s="29" t="s">
+        <v>75</v>
+      </c>
+      <c r="AH12" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="AI12" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="AJ12" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="AK12" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="AL12" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="AM12" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="AN12" s="29" t="s">
+        <v>76</v>
+      </c>
+      <c r="AO12" s="29" t="s">
+        <v>116</v>
+      </c>
+      <c r="AP12" s="29" t="s">
         <v>72</v>
       </c>
-      <c r="W6" s="29" t="s">
+      <c r="AQ12" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="AR12" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="AS12" s="29" t="s">
+        <v>132</v>
+      </c>
+      <c r="AT12" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="AU12" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="AV12" s="29" t="s">
+        <v>78</v>
+      </c>
+      <c r="AW12" s="29" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="13" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="A13" s="29" t="s">
+        <v>117</v>
+      </c>
+      <c r="B13" s="29" t="s">
+        <v>133</v>
+      </c>
+      <c r="C13" s="29" t="s">
+        <v>134</v>
+      </c>
+      <c r="D13" s="29" t="s">
+        <v>135</v>
+      </c>
+      <c r="E13" s="29" t="s">
+        <v>136</v>
+      </c>
+      <c r="F13" s="29" t="s">
+        <v>137</v>
+      </c>
+      <c r="G13" s="29" t="s">
+        <v>138</v>
+      </c>
+      <c r="H13" s="29">
+        <v>23038</v>
+      </c>
+      <c r="I13" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="J13" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="K13" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="L13" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="M13" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="N13" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="O13" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="P13" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q13" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="R13" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="S13" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="T13" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="U13" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="V13" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="W13" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="X13" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="Y13" s="29">
+        <v>2</v>
+      </c>
+      <c r="Z13" s="29">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="AB13" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="AC13" s="29" t="s">
+        <v>91</v>
+      </c>
+      <c r="AD13" s="29" t="s">
+        <v>78</v>
+      </c>
+      <c r="AE13" s="29" t="s">
+        <v>139</v>
+      </c>
+      <c r="AF13" s="29" t="s">
+        <v>140</v>
+      </c>
+      <c r="AG13" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="AH13" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="AI13" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="AJ13" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="AK13" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="AL13" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="AM13" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="AN13" s="29" t="s">
+        <v>76</v>
+      </c>
+      <c r="AO13" s="29" t="s">
+        <v>78</v>
+      </c>
+      <c r="AP13" s="29" t="s">
         <v>72</v>
       </c>
-      <c r="X6" s="29" t="s">
-        <v>72</v>
-      </c>
-      <c r="Y6" s="29">
-        <v>0</v>
-      </c>
-      <c r="Z6" s="29">
-        <v>0</v>
-      </c>
-      <c r="AA6" s="29" t="s">
-        <v>71</v>
-      </c>
-      <c r="AB6" s="29" t="s">
-        <v>71</v>
-      </c>
-      <c r="AC6" s="29" t="s">
-        <v>74</v>
-      </c>
-      <c r="AD6" s="29" t="s">
-        <v>75</v>
-      </c>
-      <c r="AE6" s="29" t="s">
-        <v>89</v>
-      </c>
-      <c r="AF6" s="29" t="s">
-        <v>72</v>
-      </c>
-      <c r="AG6" s="29" t="s">
-        <v>77</v>
-      </c>
-      <c r="AH6" s="29" t="s">
-        <v>72</v>
-      </c>
-      <c r="AI6" s="29" t="s">
-        <v>72</v>
-      </c>
-      <c r="AJ6" s="29" t="s">
-        <v>72</v>
-      </c>
-      <c r="AK6" s="29" t="s">
-        <v>72</v>
-      </c>
-      <c r="AL6" s="29" t="s">
-        <v>72</v>
-      </c>
-      <c r="AM6" s="29" t="s">
-        <v>72</v>
-      </c>
-      <c r="AN6" s="29" t="s">
-        <v>78</v>
-      </c>
-      <c r="AO6" s="29" t="s">
-        <v>75</v>
-      </c>
-      <c r="AP6" s="29" t="s">
-        <v>74</v>
-      </c>
-      <c r="AQ6" s="29" t="s">
-        <v>74</v>
-      </c>
-      <c r="AR6" s="29" t="s">
-        <v>74</v>
-      </c>
-      <c r="AS6" s="29" t="s">
-        <v>75</v>
-      </c>
-      <c r="AT6" s="29" t="s">
-        <v>73</v>
-      </c>
-      <c r="AU6" s="29" t="s">
-        <v>73</v>
-      </c>
-      <c r="AV6" s="29" t="s">
-        <v>75</v>
-      </c>
-      <c r="AW6" s="29" t="s">
+      <c r="AQ13" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="AR13" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="AS13" s="29" t="s">
+        <v>85</v>
+      </c>
+      <c r="AT13" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="AU13" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="AV13" s="29" t="s">
+        <v>78</v>
+      </c>
+      <c r="AW13" s="29" t="s">
         <v>79</v>
       </c>
     </row>
